--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N79_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N79_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.23818884108082</v>
+        <v>3.126205686675633</v>
       </c>
       <c r="D2" t="n">
-        <v>19.70717130355482</v>
+        <v>3.202415336827659</v>
       </c>
       <c r="E2" t="n">
-        <v>12.91588209782081</v>
+        <v>2.098830840895882</v>
       </c>
       <c r="F2" t="n">
-        <v>12.64995967245211</v>
+        <v>2.055618446773467</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.5562726403769</v>
+        <v>6.590394304061247</v>
       </c>
       <c r="D3" t="n">
-        <v>40.14156294908187</v>
+        <v>6.523003979225805</v>
       </c>
       <c r="E3" t="n">
-        <v>12.91588209782081</v>
+        <v>2.098830840895882</v>
       </c>
       <c r="F3" t="n">
-        <v>12.64995967245211</v>
+        <v>2.055618446773467</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.14184790150221</v>
+        <v>8.14805028399411</v>
       </c>
       <c r="D4" t="n">
-        <v>50.09670926286514</v>
+        <v>8.140715255215586</v>
       </c>
       <c r="E4" t="n">
-        <v>12.91588209782081</v>
+        <v>2.098830840895882</v>
       </c>
       <c r="F4" t="n">
-        <v>12.64995967245211</v>
+        <v>2.055618446773467</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
